--- a/01_Raw Data/outputs/reports/event_scope_v2_manual_review.xlsx
+++ b/01_Raw Data/outputs/reports/event_scope_v2_manual_review.xlsx
@@ -20,6 +20,7 @@
     <definedName name="ExternalData_1" localSheetId="0" hidden="1">event_scope_v2_manual_review!$A$1:$M$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="206">
   <si>
     <t>case</t>
   </si>
@@ -103,9 +104,6 @@
   </si>
   <si>
     <t>sample_unchanged</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>lombok_2018</t>
@@ -819,15 +817,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -846,7 +841,7 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -876,16 +871,7 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -975,6 +961,15 @@
       </fill>
       <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1011,22 +1006,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4DF0FD98-0300-44B6-929F-C49B5B28A1FD}" name="event_scope_v2_manual_review" displayName="event_scope_v2_manual_review" ref="A1:M85" tableType="queryTable" totalsRowShown="0" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4DF0FD98-0300-44B6-929F-C49B5B28A1FD}" name="event_scope_v2_manual_review" displayName="event_scope_v2_manual_review" ref="A1:M85" tableType="queryTable" totalsRowShown="0" dataDxfId="13">
   <autoFilter ref="A1:M85" xr:uid="{4DF0FD98-0300-44B6-929F-C49B5B28A1FD}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{A5F2477B-9770-4606-A0F9-D2035F8791D7}" uniqueName="1" name="case" queryTableFieldId="1" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{26487AAF-1FE5-4258-8F12-A75BB076EEB6}" uniqueName="2" name="id" queryTableFieldId="2" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{0E206073-744F-4EA5-B02C-AFC19C8FDEEB}" uniqueName="3" name="created_at_source" queryTableFieldId="3" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{D1632F14-613A-49CE-8E4A-D5E989872853}" uniqueName="4" name="text" queryTableFieldId="4" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{1D4F980E-1755-4D37-9C5E-97A49D710A42}" uniqueName="5" name="v1_scope" queryTableFieldId="5" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{AA0DCEC4-4115-410B-8B9E-E5711C1558AA}" uniqueName="6" name="v2_scope" queryTableFieldId="6" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{C986F17A-62BF-46B8-BB17-EF20E86E8486}" uniqueName="7" name="v2_reason" queryTableFieldId="7" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{E3DCB368-02E4-4772-9CBB-314A12A046F3}" uniqueName="8" name="v1_to_v2_changed" queryTableFieldId="8" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{4317A000-FE05-4142-982E-7F655DF03F79}" uniqueName="9" name="review_stratum" queryTableFieldId="9" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{6F114BA5-B27F-48FC-B58C-E85B5A470656}" uniqueName="10" name="manual_scope" queryTableFieldId="10" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{BAD91707-688B-489B-9C61-8DEB393B24BD}" uniqueName="11" name="manual_notes" queryTableFieldId="11" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{A5F2477B-9770-4606-A0F9-D2035F8791D7}" uniqueName="1" name="case" queryTableFieldId="1" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{26487AAF-1FE5-4258-8F12-A75BB076EEB6}" uniqueName="2" name="id" queryTableFieldId="2" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{0E206073-744F-4EA5-B02C-AFC19C8FDEEB}" uniqueName="3" name="created_at_source" queryTableFieldId="3" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{D1632F14-613A-49CE-8E4A-D5E989872853}" uniqueName="4" name="text" queryTableFieldId="4" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{1D4F980E-1755-4D37-9C5E-97A49D710A42}" uniqueName="5" name="v1_scope" queryTableFieldId="5" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{AA0DCEC4-4115-410B-8B9E-E5711C1558AA}" uniqueName="6" name="v2_scope" queryTableFieldId="6" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{C986F17A-62BF-46B8-BB17-EF20E86E8486}" uniqueName="7" name="v2_reason" queryTableFieldId="7" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{E3DCB368-02E4-4772-9CBB-314A12A046F3}" uniqueName="8" name="v1_to_v2_changed" queryTableFieldId="8" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{4317A000-FE05-4142-982E-7F655DF03F79}" uniqueName="9" name="review_stratum" queryTableFieldId="9" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{6F114BA5-B27F-48FC-B58C-E85B5A470656}" uniqueName="10" name="manual_scope" queryTableFieldId="10" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{BAD91707-688B-489B-9C61-8DEB393B24BD}" uniqueName="11" name="manual_notes" queryTableFieldId="11" dataDxfId="2"/>
     <tableColumn id="12" xr3:uid="{2636B57D-1667-4A46-82C9-A4940A4D2E02}" uniqueName="12" name="reviewer" queryTableFieldId="12" dataDxfId="1"/>
-    <tableColumn id="13" xr3:uid="{57CF5160-D42C-4366-AD9A-05BF47CFA464}" uniqueName="13" name="reviewed_at" queryTableFieldId="13" dataDxfId="5"/>
+    <tableColumn id="13" xr3:uid="{57CF5160-D42C-4366-AD9A-05BF47CFA464}" uniqueName="13" name="reviewed_at" queryTableFieldId="13" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1391,13 +1386,13 @@
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="1">
         <v>1.0474908818785116E+18</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -1409,176 +1404,176 @@
       <c r="G2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="2" t="b">
+      <c r="H2" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K2" s="3"/>
+      <c r="J2" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K2" s="2"/>
       <c r="L2" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M2" s="4">
+        <v>197</v>
+      </c>
+      <c r="M2" s="3">
         <v>46306</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1.0265040855481016E+18</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="2">
-        <v>1.0265040855481016E+18</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="E3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="2" t="b">
+      <c r="H3" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K3" s="3"/>
+      <c r="J3" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K3" s="2"/>
       <c r="L3" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M3" s="4">
+        <v>197</v>
+      </c>
+      <c r="M3" s="3">
         <v>46307</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="2">
+        <v>19</v>
+      </c>
+      <c r="B4" s="1">
         <v>1.026495472922284E+18</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="E4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="2" t="b">
+      <c r="H4" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="K4" s="3"/>
+      <c r="J4" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="K4" s="2"/>
       <c r="L4" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M4" s="4">
+        <v>197</v>
+      </c>
+      <c r="M4" s="3">
         <v>46308</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="2">
+        <v>19</v>
+      </c>
+      <c r="B5" s="1">
         <v>1.0264215297754931E+18</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="E5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="2" t="b">
+      <c r="H5" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K5" s="3"/>
+      <c r="J5" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K5" s="2"/>
       <c r="L5" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M5" s="4">
+        <v>197</v>
+      </c>
+      <c r="M5" s="3">
         <v>46309</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="2">
+        <v>19</v>
+      </c>
+      <c r="B6" s="1">
         <v>1.0264110694665339E+18</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="E6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="2" t="b">
+      <c r="H6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K6" s="3"/>
+      <c r="J6" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K6" s="2"/>
       <c r="L6" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M6" s="4">
+        <v>197</v>
+      </c>
+      <c r="M6" s="3">
         <v>46310</v>
       </c>
     </row>
@@ -1586,38 +1581,38 @@
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="1">
         <v>1.0459742324153631E+18</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>32</v>
-      </c>
       <c r="E7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="2" t="b">
+      <c r="H7" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="K7" s="3"/>
+      <c r="J7" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="K7" s="2"/>
       <c r="L7" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M7" s="4">
+        <v>197</v>
+      </c>
+      <c r="M7" s="3">
         <v>46311</v>
       </c>
     </row>
@@ -1625,272 +1620,272 @@
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <v>1.0459556874051133E+18</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="E8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="2" t="b">
+      <c r="H8" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K8" s="3"/>
+      <c r="J8" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K8" s="2"/>
       <c r="L8" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M8" s="4">
+        <v>197</v>
+      </c>
+      <c r="M8" s="3">
         <v>46312</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1.9946629526629627E+18</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="2">
-        <v>1.9946629526629627E+18</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H9" s="2" t="b">
+      <c r="H9" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K9" s="3"/>
+      <c r="J9" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K9" s="2"/>
       <c r="L9" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M9" s="4">
+        <v>197</v>
+      </c>
+      <c r="M9" s="3">
         <v>46313</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="2">
+        <v>34</v>
+      </c>
+      <c r="B10" s="1">
         <v>1.9945770401511222E+18</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="E10" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H10" s="2" t="b">
+        <v>37</v>
+      </c>
+      <c r="H10" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K10" s="3"/>
+      <c r="J10" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K10" s="2"/>
       <c r="L10" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M10" s="4">
+        <v>197</v>
+      </c>
+      <c r="M10" s="3">
         <v>46314</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="2">
+        <v>19</v>
+      </c>
+      <c r="B11" s="1">
         <v>1.0263055899309957E+18</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="E11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H11" s="2" t="b">
+      <c r="H11" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="K11" s="3"/>
+      <c r="J11" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="K11" s="2"/>
       <c r="L11" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M11" s="4">
+        <v>197</v>
+      </c>
+      <c r="M11" s="3">
         <v>46315</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="2">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1">
         <v>1.0290217404735447E+18</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="E12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H12" s="2" t="b">
+      <c r="H12" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K12" s="3"/>
+      <c r="J12" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K12" s="2"/>
       <c r="L12" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M12" s="4">
+        <v>197</v>
+      </c>
+      <c r="M12" s="3">
         <v>46316</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="2">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1">
         <v>1.0290067012009902E+18</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="E13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H13" s="2" t="b">
+      <c r="H13" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K13" s="3"/>
+      <c r="J13" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K13" s="2"/>
       <c r="L13" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M13" s="4">
+        <v>197</v>
+      </c>
+      <c r="M13" s="3">
         <v>46317</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="2">
+        <v>19</v>
+      </c>
+      <c r="B14" s="1">
         <v>1.0289140507748516E+18</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="E14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H14" s="2" t="b">
+      <c r="H14" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K14" s="3"/>
+      <c r="J14" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K14" s="2"/>
       <c r="L14" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M14" s="4">
+        <v>197</v>
+      </c>
+      <c r="M14" s="3">
         <v>46318</v>
       </c>
     </row>
@@ -1898,38 +1893,38 @@
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="1">
         <v>1.047046556623487E+18</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="E15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H15" s="2" t="b">
+      <c r="H15" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K15" s="3"/>
+      <c r="J15" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K15" s="2"/>
       <c r="L15" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M15" s="4">
+        <v>197</v>
+      </c>
+      <c r="M15" s="3">
         <v>46319</v>
       </c>
     </row>
@@ -1937,116 +1932,116 @@
       <c r="A16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="1">
         <v>1.0470405147117937E+18</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="E16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H16" s="2" t="b">
+      <c r="H16" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K16" s="3"/>
+      <c r="J16" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K16" s="2"/>
       <c r="L16" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M16" s="4">
+        <v>197</v>
+      </c>
+      <c r="M16" s="3">
         <v>46320</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="2">
+        <v>34</v>
+      </c>
+      <c r="B17" s="1">
         <v>1.996195214365758E+18</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="E17" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H17" s="2" t="b">
+        <v>37</v>
+      </c>
+      <c r="H17" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K17" s="3"/>
+      <c r="J17" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K17" s="2"/>
       <c r="L17" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M17" s="4">
+        <v>197</v>
+      </c>
+      <c r="M17" s="3">
         <v>46321</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="2">
+        <v>34</v>
+      </c>
+      <c r="B18" s="1">
         <v>1.9961801132900887E+18</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="3" t="s">
         <v>54</v>
       </c>
+      <c r="D18" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="E18" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H18" s="2" t="b">
+        <v>37</v>
+      </c>
+      <c r="H18" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K18" s="3"/>
+      <c r="J18" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K18" s="2"/>
       <c r="L18" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M18" s="4">
+        <v>197</v>
+      </c>
+      <c r="M18" s="3">
         <v>46322</v>
       </c>
     </row>
@@ -2054,77 +2049,77 @@
       <c r="A19" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="1">
         <v>1.0468402089923502E+18</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="E19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H19" s="2" t="b">
+      <c r="H19" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K19" s="3"/>
+      <c r="J19" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K19" s="2"/>
       <c r="L19" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M19" s="4">
+        <v>197</v>
+      </c>
+      <c r="M19" s="3">
         <v>46323</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1">
         <v>1.0288062376625275E+18</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="E20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H20" s="2" t="b">
+      <c r="H20" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K20" s="3"/>
+      <c r="J20" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K20" s="2"/>
       <c r="L20" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M20" s="4">
+        <v>197</v>
+      </c>
+      <c r="M20" s="3">
         <v>46324</v>
       </c>
     </row>
@@ -2132,389 +2127,389 @@
       <c r="A21" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="1">
         <v>1.0469768560613499E+18</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="E21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H21" s="2" t="b">
+      <c r="H21" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K21" s="3"/>
+      <c r="J21" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K21" s="2"/>
       <c r="L21" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M21" s="4">
+        <v>197</v>
+      </c>
+      <c r="M21" s="3">
         <v>46325</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" s="2">
+        <v>34</v>
+      </c>
+      <c r="B22" s="1">
         <v>1.9960817203582694E+18</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H22" s="2" t="b">
+      <c r="H22" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K22" s="3"/>
+      <c r="J22" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K22" s="2"/>
       <c r="L22" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M22" s="4">
+        <v>197</v>
+      </c>
+      <c r="M22" s="3">
         <v>46326</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="216" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" s="2">
+        <v>34</v>
+      </c>
+      <c r="B23" s="1">
         <v>1.9960641910364163E+18</v>
       </c>
       <c r="C23" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="E23" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H23" s="2" t="b">
+        <v>37</v>
+      </c>
+      <c r="H23" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K23" s="3"/>
+      <c r="J23" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K23" s="2"/>
       <c r="L23" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M23" s="4">
+        <v>197</v>
+      </c>
+      <c r="M23" s="3">
         <v>46327</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" s="2">
+        <v>34</v>
+      </c>
+      <c r="B24" s="1">
         <v>1.9960591596542487E+18</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="E24" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H24" s="2" t="b">
+        <v>37</v>
+      </c>
+      <c r="H24" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K24" s="3"/>
+      <c r="J24" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K24" s="2"/>
       <c r="L24" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M24" s="4">
+        <v>197</v>
+      </c>
+      <c r="M24" s="3">
         <v>46328</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B25" s="2">
+        <v>34</v>
+      </c>
+      <c r="B25" s="1">
         <v>1.9960512306999828E+18</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="E25" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H25" s="2" t="b">
+        <v>37</v>
+      </c>
+      <c r="H25" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J25" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K25" s="3"/>
+      <c r="J25" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K25" s="2"/>
       <c r="L25" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M25" s="4">
+        <v>197</v>
+      </c>
+      <c r="M25" s="3">
         <v>46329</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="2">
+        <v>34</v>
+      </c>
+      <c r="B26" s="1">
         <v>1.9960467317092191E+18</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="E26" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H26" s="2" t="b">
+        <v>37</v>
+      </c>
+      <c r="H26" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K26" s="3"/>
+      <c r="J26" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K26" s="2"/>
       <c r="L26" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M26" s="4">
+        <v>197</v>
+      </c>
+      <c r="M26" s="3">
         <v>46330</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="2">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1">
         <v>1.9960344763430016E+18</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="E27" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H27" s="2" t="b">
+        <v>63</v>
+      </c>
+      <c r="H27" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K27" s="3"/>
+      <c r="J27" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K27" s="2"/>
       <c r="L27" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M27" s="4">
+        <v>197</v>
+      </c>
+      <c r="M27" s="3">
         <v>46331</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="2">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1">
         <v>1.9960503930388319E+18</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="E28" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H28" s="2" t="b">
+        <v>37</v>
+      </c>
+      <c r="H28" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J28" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K28" s="3"/>
+      <c r="J28" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K28" s="2"/>
       <c r="L28" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M28" s="4">
+        <v>197</v>
+      </c>
+      <c r="M28" s="3">
         <v>46332</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="2">
+        <v>34</v>
+      </c>
+      <c r="B29" s="1">
         <v>1.9961102736028227E+18</v>
       </c>
       <c r="C29" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="E29" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H29" s="2" t="b">
+        <v>37</v>
+      </c>
+      <c r="H29" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K29" s="3"/>
+      <c r="J29" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K29" s="2"/>
       <c r="L29" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M29" s="4">
+        <v>197</v>
+      </c>
+      <c r="M29" s="3">
         <v>46333</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B30" s="2">
+        <v>34</v>
+      </c>
+      <c r="B30" s="1">
         <v>1.9960900883890504E+18</v>
       </c>
       <c r="C30" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="E30" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H30" s="2" t="b">
+        <v>37</v>
+      </c>
+      <c r="H30" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J30" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K30" s="3"/>
+      <c r="J30" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K30" s="2"/>
       <c r="L30" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M30" s="4">
+        <v>197</v>
+      </c>
+      <c r="M30" s="3">
         <v>46334</v>
       </c>
     </row>
@@ -2522,350 +2517,350 @@
       <c r="A31" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31" s="1">
         <v>1.047288115033858E+18</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="E31" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H31" s="2" t="b">
+      <c r="H31" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J31" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K31" s="3"/>
+      <c r="J31" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K31" s="2"/>
       <c r="L31" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M31" s="4">
+        <v>197</v>
+      </c>
+      <c r="M31" s="3">
         <v>46335</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32" s="2">
+        <v>34</v>
+      </c>
+      <c r="B32" s="1">
         <v>1.9964074640452119E+18</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="E32" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H32" s="2" t="b">
+        <v>37</v>
+      </c>
+      <c r="H32" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K32" s="3"/>
+      <c r="J32" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K32" s="2"/>
       <c r="L32" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M32" s="4">
+        <v>197</v>
+      </c>
+      <c r="M32" s="3">
         <v>46336</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" s="2">
+        <v>34</v>
+      </c>
+      <c r="B33" s="1">
         <v>1.9963951506215283E+18</v>
       </c>
       <c r="C33" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="E33" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H33" s="2" t="b">
+        <v>37</v>
+      </c>
+      <c r="H33" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K33" s="3"/>
+      <c r="J33" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K33" s="2"/>
       <c r="L33" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M33" s="4">
+        <v>197</v>
+      </c>
+      <c r="M33" s="3">
         <v>46337</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B34" s="2">
+        <v>19</v>
+      </c>
+      <c r="B34" s="1">
         <v>1.0293189813189304E+18</v>
       </c>
       <c r="C34" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="E34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F34" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H34" s="2" t="b">
+      <c r="H34" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J34" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K34" s="3"/>
+      <c r="J34" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K34" s="2"/>
       <c r="L34" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M34" s="4">
+        <v>197</v>
+      </c>
+      <c r="M34" s="3">
         <v>46338</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35" s="2">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1">
         <v>1.9964917208429614E+18</v>
       </c>
       <c r="C35" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="E35" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H35" s="2" t="b">
+        <v>63</v>
+      </c>
+      <c r="H35" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K35" s="3"/>
+      <c r="J35" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K35" s="2"/>
       <c r="L35" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M35" s="4">
+        <v>197</v>
+      </c>
+      <c r="M35" s="3">
         <v>46339</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" s="2">
+        <v>34</v>
+      </c>
+      <c r="B36" s="1">
         <v>1.9964447138855078E+18</v>
       </c>
       <c r="C36" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="E36" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H36" s="2" t="b">
+        <v>63</v>
+      </c>
+      <c r="H36" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J36" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K36" s="3"/>
+      <c r="J36" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K36" s="2"/>
       <c r="L36" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M36" s="4">
+        <v>197</v>
+      </c>
+      <c r="M36" s="3">
         <v>46340</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B37" s="2">
+        <v>19</v>
+      </c>
+      <c r="B37" s="1">
         <v>1.0293681217804042E+18</v>
       </c>
       <c r="C37" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="E37" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H37" s="2" t="b">
+      <c r="H37" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J37" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K37" s="3"/>
+      <c r="J37" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K37" s="2"/>
       <c r="L37" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M37" s="4">
+        <v>197</v>
+      </c>
+      <c r="M37" s="3">
         <v>46341</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B38" s="2">
+        <v>19</v>
+      </c>
+      <c r="B38" s="1">
         <v>1.0293573259020124E+18</v>
       </c>
       <c r="C38" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="E38" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H38" s="2" t="b">
+      <c r="H38" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J38" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K38" s="3"/>
+      <c r="J38" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K38" s="2"/>
       <c r="L38" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M38" s="4">
+        <v>197</v>
+      </c>
+      <c r="M38" s="3">
         <v>46342</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B39" s="2">
+        <v>34</v>
+      </c>
+      <c r="B39" s="1">
         <v>1.9965363075864003E+18</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="E39" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H39" s="2" t="b">
+        <v>37</v>
+      </c>
+      <c r="H39" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J39" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K39" s="3"/>
+      <c r="J39" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K39" s="2"/>
       <c r="L39" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M39" s="4">
+        <v>197</v>
+      </c>
+      <c r="M39" s="3">
         <v>46343</v>
       </c>
     </row>
@@ -2873,1799 +2868,1799 @@
       <c r="A40" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B40" s="1">
         <v>1.0471779122254152E+18</v>
       </c>
       <c r="C40" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="E40" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H40" s="2" t="b">
+      <c r="H40" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J40" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K40" s="3"/>
+      <c r="J40" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K40" s="2"/>
       <c r="L40" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M40" s="4">
+        <v>197</v>
+      </c>
+      <c r="M40" s="3">
         <v>46344</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B41" s="2">
+        <v>34</v>
+      </c>
+      <c r="B41" s="1">
         <v>1.9947904540517135E+18</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="E41" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="F41" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H41" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I41" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H41" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K41" s="3"/>
+      <c r="J41" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K41" s="2"/>
       <c r="L41" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M41" s="4">
+        <v>197</v>
+      </c>
+      <c r="M41" s="3">
         <v>46345</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B42" s="2">
+        <v>34</v>
+      </c>
+      <c r="B42" s="1">
         <v>1.9947337481775724E+18</v>
       </c>
       <c r="C42" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="E42" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H42" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I42" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F42" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H42" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K42" s="3"/>
+      <c r="J42" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K42" s="2"/>
       <c r="L42" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M42" s="4">
+        <v>197</v>
+      </c>
+      <c r="M42" s="3">
         <v>46346</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B43" s="2">
+        <v>34</v>
+      </c>
+      <c r="B43" s="1">
         <v>1.9947320709718717E+18</v>
       </c>
       <c r="C43" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="E43" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H43" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I43" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H43" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K43" s="3"/>
+      <c r="J43" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K43" s="2"/>
       <c r="L43" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M43" s="4">
+        <v>197</v>
+      </c>
+      <c r="M43" s="3">
         <v>46347</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B44" s="2">
+        <v>34</v>
+      </c>
+      <c r="B44" s="1">
         <v>1.9947233348448136E+18</v>
       </c>
       <c r="C44" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="E44" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H44" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I44" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F44" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H44" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K44" s="3"/>
+      <c r="J44" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K44" s="2"/>
       <c r="L44" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M44" s="4">
+        <v>197</v>
+      </c>
+      <c r="M44" s="3">
         <v>46348</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B45" s="2">
+        <v>34</v>
+      </c>
+      <c r="B45" s="1">
         <v>1.9945833902183263E+18</v>
       </c>
       <c r="C45" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="E45" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H45" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I45" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F45" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H45" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K45" s="3"/>
+      <c r="J45" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K45" s="2"/>
       <c r="L45" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M45" s="4">
+        <v>197</v>
+      </c>
+      <c r="M45" s="3">
         <v>46349</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B46" s="2">
+        <v>34</v>
+      </c>
+      <c r="B46" s="1">
         <v>1.9947261486648691E+18</v>
       </c>
       <c r="C46" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="E46" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H46" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I46" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F46" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H46" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K46" s="3"/>
+      <c r="J46" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K46" s="2"/>
       <c r="L46" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M46" s="4">
+        <v>197</v>
+      </c>
+      <c r="M46" s="3">
         <v>46350</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B47" s="2">
+        <v>34</v>
+      </c>
+      <c r="B47" s="1">
         <v>1.9962270703182851E+18</v>
       </c>
       <c r="C47" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="E47" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H47" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I47" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F47" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H47" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K47" s="3"/>
+      <c r="J47" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K47" s="2"/>
       <c r="L47" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M47" s="4">
+        <v>197</v>
+      </c>
+      <c r="M47" s="3">
         <v>46351</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B48" s="2">
+        <v>34</v>
+      </c>
+      <c r="B48" s="1">
         <v>1.9962074965503183E+18</v>
       </c>
       <c r="C48" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="E48" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H48" s="2" t="b">
+        <v>118</v>
+      </c>
+      <c r="H48" s="1" t="b">
         <v>1</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K48" s="3"/>
+        <v>103</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K48" s="2"/>
       <c r="L48" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M48" s="4">
+        <v>197</v>
+      </c>
+      <c r="M48" s="3">
         <v>46352</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B49" s="2">
+        <v>34</v>
+      </c>
+      <c r="B49" s="1">
         <v>1.9961867359702226E+18</v>
       </c>
       <c r="C49" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="E49" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H49" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I49" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F49" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H49" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K49" s="3"/>
+      <c r="J49" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K49" s="2"/>
       <c r="L49" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M49" s="4">
+        <v>197</v>
+      </c>
+      <c r="M49" s="3">
         <v>46353</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B50" s="2">
+        <v>34</v>
+      </c>
+      <c r="B50" s="1">
         <v>1.9960575664184443E+18</v>
       </c>
       <c r="C50" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>123</v>
-      </c>
       <c r="E50" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H50" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I50" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F50" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H50" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K50" s="3"/>
+      <c r="J50" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K50" s="2"/>
       <c r="L50" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M50" s="4">
+        <v>197</v>
+      </c>
+      <c r="M50" s="3">
         <v>46354</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B51" s="2">
+        <v>34</v>
+      </c>
+      <c r="B51" s="1">
         <v>1.9960514352813714E+18</v>
       </c>
       <c r="C51" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="E51" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G51" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="H51" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I51" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F51" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="H51" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I51" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K51" s="3"/>
+      <c r="J51" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K51" s="2"/>
       <c r="L51" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M51" s="4">
+        <v>197</v>
+      </c>
+      <c r="M51" s="3">
         <v>46355</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B52" s="2">
+        <v>34</v>
+      </c>
+      <c r="B52" s="1">
         <v>1.9960278102811279E+18</v>
       </c>
       <c r="C52" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="E52" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H52" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I52" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F52" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H52" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K52" s="3"/>
+      <c r="J52" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K52" s="2"/>
       <c r="L52" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M52" s="4">
+        <v>197</v>
+      </c>
+      <c r="M52" s="3">
         <v>46356</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B53" s="2">
+        <v>34</v>
+      </c>
+      <c r="B53" s="1">
         <v>1.9959917011740593E+18</v>
       </c>
       <c r="C53" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>130</v>
-      </c>
       <c r="E53" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H53" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I53" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F53" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H53" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K53" s="3"/>
+      <c r="J53" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K53" s="2"/>
       <c r="L53" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M53" s="4">
+        <v>197</v>
+      </c>
+      <c r="M53" s="3">
         <v>46357</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B54" s="2">
+        <v>34</v>
+      </c>
+      <c r="B54" s="1">
         <v>1.9960662823500229E+18</v>
       </c>
       <c r="C54" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="E54" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H54" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I54" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F54" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H54" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K54" s="3"/>
+      <c r="J54" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K54" s="2"/>
       <c r="L54" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M54" s="4">
+        <v>197</v>
+      </c>
+      <c r="M54" s="3">
         <v>46358</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B55" s="2">
+        <v>34</v>
+      </c>
+      <c r="B55" s="1">
         <v>1.9960600399967357E+18</v>
       </c>
       <c r="C55" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D55" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>134</v>
-      </c>
       <c r="E55" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H55" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I55" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F55" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H55" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K55" s="3"/>
+      <c r="J55" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K55" s="2"/>
       <c r="L55" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M55" s="4">
+        <v>197</v>
+      </c>
+      <c r="M55" s="3">
         <v>46359</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B56" s="2">
+        <v>34</v>
+      </c>
+      <c r="B56" s="1">
         <v>1.9960573644207928E+18</v>
       </c>
       <c r="C56" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D56" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="E56" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H56" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I56" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F56" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H56" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K56" s="3"/>
+      <c r="J56" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K56" s="2"/>
       <c r="L56" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M56" s="4">
+        <v>197</v>
+      </c>
+      <c r="M56" s="3">
         <v>46360</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B57" s="2">
+        <v>34</v>
+      </c>
+      <c r="B57" s="1">
         <v>1.9960568730791327E+18</v>
       </c>
       <c r="C57" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="E57" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H57" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I57" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F57" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H57" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I57" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K57" s="3"/>
+      <c r="J57" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K57" s="2"/>
       <c r="L57" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M57" s="4">
+        <v>197</v>
+      </c>
+      <c r="M57" s="3">
         <v>46361</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B58" s="2">
+        <v>34</v>
+      </c>
+      <c r="B58" s="1">
         <v>1.996053484412834E+18</v>
       </c>
       <c r="C58" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="E58" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H58" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I58" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F58" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H58" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K58" s="3"/>
+      <c r="J58" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K58" s="2"/>
       <c r="L58" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M58" s="4">
+        <v>197</v>
+      </c>
+      <c r="M58" s="3">
         <v>46362</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B59" s="2">
+        <v>34</v>
+      </c>
+      <c r="B59" s="1">
         <v>1.9961430131948667E+18</v>
       </c>
       <c r="C59" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D59" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="E59" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H59" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I59" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F59" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="H59" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K59" s="3"/>
+      <c r="J59" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K59" s="2"/>
       <c r="L59" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M59" s="4">
+        <v>197</v>
+      </c>
+      <c r="M59" s="3">
         <v>46363</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B60" s="2">
+        <v>34</v>
+      </c>
+      <c r="B60" s="1">
         <v>1.9961425163334164E+18</v>
       </c>
       <c r="C60" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="E60" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H60" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I60" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F60" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H60" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I60" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K60" s="3"/>
+      <c r="J60" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K60" s="2"/>
       <c r="L60" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M60" s="4">
+        <v>197</v>
+      </c>
+      <c r="M60" s="3">
         <v>46364</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B61" s="2">
+        <v>34</v>
+      </c>
+      <c r="B61" s="1">
         <v>1.9961330311623803E+18</v>
       </c>
       <c r="C61" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="E61" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H61" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I61" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F61" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H61" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K61" s="3"/>
+      <c r="J61" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K61" s="2"/>
       <c r="L61" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M61" s="4">
+        <v>197</v>
+      </c>
+      <c r="M61" s="3">
         <v>46365</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B62" s="2">
+        <v>34</v>
+      </c>
+      <c r="B62" s="1">
         <v>1.996117001790751E+18</v>
       </c>
       <c r="C62" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D62" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="E62" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H62" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I62" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F62" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="H62" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I62" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K62" s="3"/>
+      <c r="J62" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K62" s="2"/>
       <c r="L62" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M62" s="4">
+        <v>197</v>
+      </c>
+      <c r="M62" s="3">
         <v>46366</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B63" s="2">
+        <v>34</v>
+      </c>
+      <c r="B63" s="1">
         <v>1.9964191438900188E+18</v>
       </c>
       <c r="C63" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D63" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D63" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="E63" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H63" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I63" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F63" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H63" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K63" s="3"/>
+      <c r="J63" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K63" s="2"/>
       <c r="L63" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M63" s="4">
+        <v>197</v>
+      </c>
+      <c r="M63" s="3">
         <v>46367</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B64" s="2">
+        <v>34</v>
+      </c>
+      <c r="B64" s="1">
         <v>1.9964166695986012E+18</v>
       </c>
       <c r="C64" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D64" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="E64" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H64" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I64" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F64" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H64" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K64" s="3"/>
+      <c r="J64" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K64" s="2"/>
       <c r="L64" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M64" s="4">
+        <v>197</v>
+      </c>
+      <c r="M64" s="3">
         <v>46368</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B65" s="2">
+        <v>34</v>
+      </c>
+      <c r="B65" s="1">
         <v>1.9964963514761874E+18</v>
       </c>
       <c r="C65" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D65" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D65" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="E65" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H65" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I65" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F65" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H65" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K65" s="3"/>
+      <c r="J65" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K65" s="2"/>
       <c r="L65" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M65" s="4">
+        <v>197</v>
+      </c>
+      <c r="M65" s="3">
         <v>46369</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B66" s="2">
+        <v>34</v>
+      </c>
+      <c r="B66" s="1">
         <v>1.9947517981341491E+18</v>
       </c>
       <c r="C66" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D66" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="E66" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="F66" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G66" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="F66" s="1" t="s">
+      <c r="H66" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I66" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="G66" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="H66" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I66" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="K66" s="3"/>
+      <c r="J66" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="K66" s="2"/>
       <c r="L66" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M66" s="4">
+        <v>197</v>
+      </c>
+      <c r="M66" s="3">
         <v>46370</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B67" s="2">
+        <v>34</v>
+      </c>
+      <c r="B67" s="1">
         <v>1.9947471960263601E+18</v>
       </c>
       <c r="C67" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D67" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="E67" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G67" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E67" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="H67" s="2" t="b">
+      <c r="H67" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K67" s="3"/>
+        <v>103</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K67" s="2"/>
       <c r="L67" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M67" s="4">
+        <v>197</v>
+      </c>
+      <c r="M67" s="3">
         <v>46371</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B68" s="2">
+        <v>34</v>
+      </c>
+      <c r="B68" s="1">
         <v>1.9947405240421299E+18</v>
       </c>
       <c r="C68" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D68" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>163</v>
-      </c>
       <c r="E68" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G68" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="H68" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I68" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="G68" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="H68" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K68" s="3"/>
+      <c r="J68" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K68" s="2"/>
       <c r="L68" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M68" s="4">
+        <v>197</v>
+      </c>
+      <c r="M68" s="3">
         <v>46372</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B69" s="2">
+        <v>34</v>
+      </c>
+      <c r="B69" s="1">
         <v>1.9945303602990659E+18</v>
       </c>
       <c r="C69" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D69" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="E69" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="H69" s="2" t="b">
+        <v>160</v>
+      </c>
+      <c r="H69" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="K69" s="3"/>
+        <v>103</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="K69" s="2"/>
       <c r="L69" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M69" s="4">
+        <v>197</v>
+      </c>
+      <c r="M69" s="3">
         <v>46373</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B70" s="2">
+        <v>34</v>
+      </c>
+      <c r="B70" s="1">
         <v>1.9962466992796265E+18</v>
       </c>
       <c r="C70" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D70" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D70" s="3" t="s">
-        <v>167</v>
-      </c>
       <c r="E70" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="H70" s="2" t="b">
+        <v>160</v>
+      </c>
+      <c r="H70" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="K70" s="3"/>
+        <v>103</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="K70" s="2"/>
       <c r="L70" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M70" s="4">
+        <v>197</v>
+      </c>
+      <c r="M70" s="3">
         <v>46374</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B71" s="2">
+        <v>34</v>
+      </c>
+      <c r="B71" s="1">
         <v>1.9961929963506565E+18</v>
       </c>
       <c r="C71" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D71" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="E71" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H71" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="K71" s="2"/>
+      <c r="L71" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="M71" s="3">
+        <v>46375</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B72" s="1">
+        <v>1.9961869531807296E+18</v>
+      </c>
+      <c r="C72" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="D72" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G72" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="F71" s="1" t="s">
+      <c r="H72" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I72" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="G71" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="H71" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J71" s="3" t="s">
+      <c r="J72" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K72" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="K71" s="3"/>
-      <c r="L71" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M71" s="4">
-        <v>46375</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A72" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B72" s="2">
-        <v>1.9961869531807296E+18</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="H72" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>204</v>
-      </c>
       <c r="L72" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M72" s="4">
+        <v>197</v>
+      </c>
+      <c r="M72" s="3">
         <v>46376</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B73" s="2">
+        <v>34</v>
+      </c>
+      <c r="B73" s="1">
         <v>1.9961442223119977E+18</v>
       </c>
       <c r="C73" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D73" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="E73" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="H73" s="2" t="b">
+        <v>160</v>
+      </c>
+      <c r="H73" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J73" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K73" s="3"/>
+        <v>103</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K73" s="2"/>
       <c r="L73" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M73" s="4">
+        <v>197</v>
+      </c>
+      <c r="M73" s="3">
         <v>46377</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B74" s="2">
+        <v>34</v>
+      </c>
+      <c r="B74" s="1">
         <v>1.9960055021118467E+18</v>
       </c>
       <c r="C74" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D74" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="D74" s="3" t="s">
-        <v>175</v>
-      </c>
       <c r="E74" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H74" s="2" t="b">
+        <v>118</v>
+      </c>
+      <c r="H74" s="1" t="b">
         <v>1</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J74" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K74" s="3"/>
+        <v>103</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K74" s="2"/>
       <c r="L74" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M74" s="4">
+        <v>197</v>
+      </c>
+      <c r="M74" s="3">
         <v>46378</v>
       </c>
     </row>
     <row r="75" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B75" s="2">
+        <v>34</v>
+      </c>
+      <c r="B75" s="1">
         <v>1.9960736016244081E+18</v>
       </c>
       <c r="C75" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D75" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="D75" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="E75" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="H75" s="2" t="b">
+        <v>160</v>
+      </c>
+      <c r="H75" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J75" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="K75" s="3"/>
+        <v>103</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="K75" s="2"/>
       <c r="L75" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M75" s="4">
+        <v>197</v>
+      </c>
+      <c r="M75" s="3">
         <v>46379</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B76" s="2">
+        <v>34</v>
+      </c>
+      <c r="B76" s="1">
         <v>1.9961149724519839E+18</v>
       </c>
       <c r="C76" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D76" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>179</v>
-      </c>
       <c r="E76" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G76" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="F76" s="1" t="s">
+      <c r="H76" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I76" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="G76" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="H76" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="K76" s="3"/>
+      <c r="J76" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="K76" s="2"/>
       <c r="L76" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M76" s="4">
+        <v>197</v>
+      </c>
+      <c r="M76" s="3">
         <v>46380</v>
       </c>
     </row>
     <row r="77" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B77" s="2">
+        <v>34</v>
+      </c>
+      <c r="B77" s="1">
         <v>1.9960864411942587E+18</v>
       </c>
       <c r="C77" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D77" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D77" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="E77" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="H77" s="2" t="b">
+        <v>160</v>
+      </c>
+      <c r="H77" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J77" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="K77" s="3"/>
+        <v>103</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="K77" s="2"/>
       <c r="L77" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M77" s="4">
+        <v>197</v>
+      </c>
+      <c r="M77" s="3">
         <v>46381</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B78" s="2">
+        <v>34</v>
+      </c>
+      <c r="B78" s="1">
         <v>1.9964083324004229E+18</v>
       </c>
       <c r="C78" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D78" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="D78" s="3" t="s">
-        <v>183</v>
-      </c>
       <c r="E78" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G78" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="F78" s="1" t="s">
+      <c r="H78" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I78" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="G78" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="H78" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I78" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J78" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="K78" s="3"/>
+      <c r="J78" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="K78" s="2"/>
       <c r="L78" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M78" s="4">
+        <v>197</v>
+      </c>
+      <c r="M78" s="3">
         <v>46382</v>
       </c>
     </row>
     <row r="79" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B79" s="2">
+        <v>34</v>
+      </c>
+      <c r="B79" s="1">
         <v>1.9965255303977208E+18</v>
       </c>
       <c r="C79" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D79" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D79" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="E79" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G79" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="F79" s="1" t="s">
+      <c r="H79" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I79" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="G79" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="H79" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I79" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J79" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K79" s="3" t="s">
-        <v>205</v>
+      <c r="J79" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>204</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M79" s="4">
+        <v>197</v>
+      </c>
+      <c r="M79" s="3">
         <v>46383</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B80" s="2">
+        <v>34</v>
+      </c>
+      <c r="B80" s="1">
         <v>1.9965033865949681E+18</v>
       </c>
       <c r="C80" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D80" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="D80" s="3" t="s">
-        <v>187</v>
-      </c>
       <c r="E80" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="H80" s="2" t="b">
+        <v>160</v>
+      </c>
+      <c r="H80" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J80" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="K80" s="3"/>
+        <v>103</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="K80" s="2"/>
       <c r="L80" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M80" s="4">
+        <v>197</v>
+      </c>
+      <c r="M80" s="3">
         <v>46384</v>
       </c>
     </row>
     <row r="81" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B81" s="2">
+        <v>34</v>
+      </c>
+      <c r="B81" s="1">
         <v>1.9964984952060436E+18</v>
       </c>
       <c r="C81" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D81" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="E81" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G81" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="F81" s="1" t="s">
+      <c r="H81" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I81" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="G81" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="H81" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="K81" s="3" t="s">
-        <v>206</v>
+      <c r="J81" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>205</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M81" s="4">
+        <v>197</v>
+      </c>
+      <c r="M81" s="3">
         <v>46385</v>
       </c>
     </row>
     <row r="82" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B82" s="2">
+        <v>34</v>
+      </c>
+      <c r="B82" s="1">
         <v>1.9965944034321124E+18</v>
       </c>
       <c r="C82" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D82" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="D82" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="E82" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H82" s="2" t="b">
+        <v>118</v>
+      </c>
+      <c r="H82" s="1" t="b">
         <v>1</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J82" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="K82" s="3"/>
+        <v>103</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="K82" s="2"/>
       <c r="L82" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M82" s="4">
+        <v>197</v>
+      </c>
+      <c r="M82" s="3">
         <v>46386</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B83" s="2">
+        <v>34</v>
+      </c>
+      <c r="B83" s="1">
         <v>1.9963520097763044E+18</v>
       </c>
       <c r="C83" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D83" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="E83" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="H83" s="2" t="b">
+        <v>160</v>
+      </c>
+      <c r="H83" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="K83" s="3"/>
+        <v>103</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="K83" s="2"/>
       <c r="L83" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M83" s="4">
+        <v>197</v>
+      </c>
+      <c r="M83" s="3">
         <v>46387</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B84" s="2">
+        <v>34</v>
+      </c>
+      <c r="B84" s="1">
         <v>1.9963104466102152E+18</v>
       </c>
       <c r="C84" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D84" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="D84" s="3" t="s">
-        <v>195</v>
-      </c>
       <c r="E84" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G84" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="F84" s="1" t="s">
+      <c r="H84" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I84" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="G84" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="H84" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I84" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J84" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="K84" s="3"/>
+      <c r="J84" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="K84" s="2"/>
       <c r="L84" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M84" s="4">
+        <v>197</v>
+      </c>
+      <c r="M84" s="3">
         <v>46388</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B85" s="2">
+        <v>34</v>
+      </c>
+      <c r="B85" s="1">
         <v>1.9962653175475203E+18</v>
       </c>
       <c r="C85" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D85" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D85" s="3" t="s">
-        <v>197</v>
-      </c>
       <c r="E85" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="H85" s="2" t="b">
+        <v>160</v>
+      </c>
+      <c r="H85" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J85" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="K85" s="3"/>
+        <v>103</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="K85" s="2"/>
       <c r="L85" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M85" s="4">
+        <v>197</v>
+      </c>
+      <c r="M85" s="3">
         <v>46389</v>
       </c>
     </row>
